--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -17,7 +17,7 @@
     <t>⚡ SecureVault – Load Test Report</t>
   </si>
   <si>
-    <t>Generated: 19/8/2026, 9:40:44 am  |  Tool: k6 Load Testing Framework</t>
+    <t>Generated: 19/8/2026, 11:36:11 am  |  Tool: k6 Load Testing Framework</t>
   </si>
   <si>
     <t>Metric</t>
